--- a/www/download/COUNTRY.LVA.EXI382.xlsx
+++ b/www/download/COUNTRY.LVA.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Letônia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24406932515337</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24406932515337</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24406932515337</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24406932515337</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24407055214724</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24407055214724</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24407055214724</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24407055214724</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24407055214724</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24407055214724</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24407055214724</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24407055214724</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24407055214724</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24407055214724</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24407055214724</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24407055214724</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24407055214724</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24407055214724</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24407055214724</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24407055214724</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24407055214724</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24407055214724</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24407055214724</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24407055214724</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24407055214724</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24407055214724</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24407055214724</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1.338</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1.105</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1.051</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>1.034</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0.965</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1.016</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.984</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>1.004</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>1.028</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>1.072</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>1.079</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>1.138</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>1.073</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>1.055</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0.908</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>0.802</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>0.853</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0.922</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0.871</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>0.976</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0.923</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>1.051</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>1.112</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>1.097</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>1.134</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1.186</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.876</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.842</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0.841</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0.793</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.849</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.844</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.858</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.898</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.913</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.933</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.961</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>1.012</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.961</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>0.953</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0.81</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>0.713</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>0.763</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0.826</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0.787</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>0.874</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>0.826</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>0.938</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>0.994</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>0.996</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>1.022</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2795.286</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2321.361</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2355.422</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2319.763</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2171.498</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2289.441</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2215.011</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2286.728</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2331.579</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>2355.983</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2344.863</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2371.724</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2501.374</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2324.75</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>2214.72</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>1870.716</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>1727.862</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1632.157</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>1739.721</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>1894.692</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>1792.556</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>2012.28</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>1907.56</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>2169.817</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2309.447</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>2275.276</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2356.7</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2482.216</t>
+          <t>3041555384.6184</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1295.763</t>
+          <t>2767972070.11735</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1413.372</t>
+          <t>3059529501.44641</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1450.843</t>
+          <t>2907948123.75234</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1384.943</t>
+          <t>3281549967.85581</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1506.815</t>
+          <t>3384478992.77658</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1561.965</t>
+          <t>3162675772.806</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1595.346</t>
+          <t>3105303241.27577</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1750.087</t>
+          <t>3084592180.17925</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1749.95</t>
+          <t>3425066693.00766</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1746.657</t>
+          <t>3351408347.58406</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1863.841</t>
+          <t>3366793296.25084</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1946.868</t>
+          <t>3415923582.2321</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1832.046</t>
+          <t>3410202945.23666</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1791.426</t>
+          <t>2994677430.44972</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1469.006</t>
+          <t>2459177632.95482</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1366.186</t>
+          <t>2522472477.23368</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1262.17</t>
+          <t>2578549449.11944</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1373.036</t>
+          <t>2389150272.49899</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>1698.619</t>
+          <t>2467685881.37547</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>1619.831</t>
+          <t>2451726377.9651</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>1802.726</t>
+          <t>2518491561.53488</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>1708.058</t>
+          <t>2494290187.30797</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1936.419</t>
+          <t>2904878432.81127</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2066.989</t>
+          <t>2914130368.09733</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2065.269</t>
+          <t>3016646261.98051</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2124.189</t>
+          <t>2909782702.25777</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1006405425.60579</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>709875680.474588</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>790936112.842737</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>782108841.597898</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>864017215.566572</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1023029744.01071</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1005166384.67748</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1087465108.5969</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>761657184.672567</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>565064723.249503</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>670174653.363282</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>993201542.395606</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>984169363.559524</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>898097569.990835</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>666979616.196297</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>568612642.6937</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>673720379.163425</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>604748042.278389</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>632305896.532793</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>564646461.69381</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>653022810.869718</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>512079058.947308</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>647286097.158924</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>740909095.252167</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>733374253.942806</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>757315570.150955</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>589070098.777389</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1763451889.84928</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>121268671.606545</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>12324115418.3076</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>68570319.621167</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>45136329.3357009</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>373621184.557314</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>31924934.6981545</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>33539910.380101</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>416434569.531223</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>26522917.5237054</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>18487010.7020676</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>126482966.147943</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>120047884545.624</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>18756595.1757768</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>15658627.0085927</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>14283972.4474678</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>11804169.5380072</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>24743816.9957813</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>11261640.6617805</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>9767068.14201112</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>8883486.2453314</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>52459348.8277017</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>7948286.61213716</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>8967379.67658149</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>9698217.74532486</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>8623123.3659952</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>9461709.9066902</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>6262.6021774703</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>13032.5699783962</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>14420.9510830259</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>14087.3969486314</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>13346.0956986545</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>16460.4058319565</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15267.6419547068</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>15693.1487196224</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>14901.3696692626</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>14678.6618812254</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>15671.8550974492</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>16277.5313777544</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>17226.511746416</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>15804.4749283288</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>15275.1147814526</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>14463.0322570659</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>13624.8851859583</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>15558.4974523401</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>15587.8909402175</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>17327.5349215843</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>18078.8342558397</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>18716.2024464566</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>18398.948193316</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>20710.862862495</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>23421.6152769052</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>21363.9654040359</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>22054.441355289</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>11337.7098860831</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>21034.0202440076</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>25322.5753580525</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>24743.5590767899</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>29452.8785150195</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>36311.4438049484</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>34070.7201187246</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>32427.5536219817</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>29589.8189591754</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>32108.0198339431</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>33680.8890233926</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>36194.0713086499</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>38046.2567676507</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>38165.3187563351</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>33585.7538953302</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>31805.4289816668</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>33963.3533403997</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>38320.7235753094</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>34683.2449282078</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>37080.0374306145</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>41615.9642839103</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>38964.6854696464</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>40799.3306985445</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>46212.1269460591</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>49394.1330481624</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>48641.78299371</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>46063.7811023125</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1.46641780993356</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.825337922738863</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.786961016256854</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0.855039762797099</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.602911348349194</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.472894614082426</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.55393676490768</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.467031895908561</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1.29773582553755</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2.09690187335733</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1.60627135215291</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.876598978596727</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.978183910296335</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>1.03991866943706</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1.68587818352957</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1.58349162452879</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1.02782347432652</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1.08710059687817</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1.17147429358015</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2.00828711139206</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>1.48051204446283</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>2.52040522955878</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>1.63879861800028</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>1.61357207340535</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>1.81846464121432</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>1.72709145323414</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2.6060041204167</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>848.733448620131</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>809.89809523649</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>939.577230747251</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>929.974841376418</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1088.86857664363</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1204.41457971548</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1191.66139262295</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1266.85124487083</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>848.265045854228</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>619.181156311265</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>717.992986247325</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1033.72350374194</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>972.115135874478</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>934.155991253185</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>699.800247819046</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>702.164290804675</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>886.007863181748</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>848.769182144928</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>828.167513468099</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>683.650320329488</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>829.832628199823</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>585.67320076033</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>783.596341625198</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>790.071542932643</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>737.708181818185</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>760.699251868315</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>576.499592739024</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>239753307.454121</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-370285163.55278</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>63395488.6516827</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>125604515.302494</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>510823424.630907</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>675823441.261862</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>961981938.821237</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>789761135.095059</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>421785937.681292</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>385302542.991419</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>200478316.332493</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>161896096.996432</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>31814511.3189874</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>232685428.476766</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>479729602.252705</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>358566106.309479</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>535516261.094725</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>776687624.541797</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>406963927.635646</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>412556220.81668</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>509220209.228272</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>449040488.155011</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>484263237.377206</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>533698316.487771</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>537312649.355991</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>661820527.63174</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>290455646.278944</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>322701835.413828</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-346319871.972963</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>66079821.3122843</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>132757105.942341</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>506561905.406223</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>651663200.709337</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>928162484.819049</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>756957523.446046</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>403701960.157131</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>372607847.825653</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>183164558.916965</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>160372635.93841</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>12678856.8764073</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>165176943.920072</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>362383523.202703</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>245683095.152416</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>425372802.321615</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>649372948.089696</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>289174594.369703</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>297595985.90499</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>378027273.177012</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>306889129.828376</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>388473823.65098</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>444548278.345134</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>452043432.000088</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>567492133.676823</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>743116398.77751</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-82948527.9597068</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-23965291.5798162</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-2684332.66060162</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-7152590.63984688</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>4261519.22468416</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>24160240.5525249</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>33819454.0021883</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>32803611.6490134</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>18083977.5241603</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>12694695.1657664</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>17313757.415528</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>1523461.05802242</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>19135654.44258</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>67508484.5566941</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>117346079.050002</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>112883011.157064</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>110143458.77311</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>127314676.452101</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>117789333.265943</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>114960234.91169</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>131192936.05126</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>142151358.326635</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>95789413.7262261</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>89150038.1426374</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>85269217.3559031</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>94328393.9549173</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-452660752.498566</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>2093.33129356302</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1478.33770678914</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>1678.98788310791</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1725.14030915418</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1745.35979836291</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>1773.97574758527</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1851.76644931789</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>1858.51118359697</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1949.08898541051</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>1917.54328292791</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>1871.28455110312</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>1939.88447127356</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>1923.02252074243</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>1905.60224672385</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>1879.57821844576</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>1814.03556433707</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>1796.66754339783</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>1771.46666666648</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>1798.34446627417</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>2056.61644734625</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>2058.4098291379</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>2061.8069987691</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>2067.75294335064</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>2064.90892060103</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>2079.20442598906</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>2074.49642825169</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>2078.85990683547</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2088.67929240304</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2100.39902280201</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2240.91142612499</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2243.70151852186</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2250.95677412718</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2253.16504280968</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2250.57000609631</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2276.48382279759</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2268.51430239381</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2244.4346003621</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2186.96418578611</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>2198.07599629263</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>2197.27160927594</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>2165.98341563412</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>2100.05689360968</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>2059.80621008579</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>2031.82267168373</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2035.36226462134</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2038.81518809362</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2054.2155607058</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>2058.17134142738</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2061.15442761977</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>2066.93121634636</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>2064.82208079204</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>2077.57135087445</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>2073.45903805337</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>2078.39382187381</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1496.62502343581</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1940.16353288276</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2064.15385315173</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2346.76955510676</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2347.58918617156</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>3054.02670541855</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3549.83548808083</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>3644.79639644093</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>3459.86357807613</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>4021.54339355506</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>5488.80154947324</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>6041.91044926249</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>7422.03373263629</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>7579.94629873409</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>7706.52070883767</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>9225.00705124682</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>10774.2591228868</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>12416.7604808104</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>12809.6332119438</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>13262.4884988046</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>14932.0538153553</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>15517.0583797197</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>16728.273684735</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17802.0809509809</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>18348.2105608231</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>18908.8382261437</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>14946.0487530541</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>425295421.463131</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>535748617.553136</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>573165229.556654</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>641935442.323738</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>609291037.955272</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>653254925.621599</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>664450781.876031</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>612193146.495972</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>553991599.754865</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>584661464.027736</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>675458999.470103</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>560263233.901857</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>577591405.420584</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>566572606.931578</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>565147114.894931</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>541581266.124715</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>572265222.02817</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>644322768.726838</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>620364503.115107</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>654070960.055168</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>637083365.482528</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>673578049.618463</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>720545972.344038</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>832963754.045423</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>821972139.397623</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>856259586.410881</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>635956463.459576</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1753.05147784389</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2494.62634259988</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2744.77466198326</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>3356.88323561126</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>3254.43050970168</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>3951.98601002118</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4815.88815894512</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>4983.57519769582</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>5163.75345860393</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>6345.74394596261</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>8044.41908139397</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>10680.3974465686</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>13068.444005033</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>11616.8899793908</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>8198.04549599957</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>9718.70020843573</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>12318.5798880217</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>13948.7809536075</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>14108.696821907</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>14170.2734371064</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>15485.8083809622</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>15407.9222634222</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>16956.5709861884</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>18103.5190708833</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>18682.1107174794</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>19433.9734478675</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>15687.546318881</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2795.286</t>
+          <t>810321043.892256</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2321.361</t>
+          <t>278095947.307833</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2355.422</t>
+          <t>763964573.683226</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2319.763</t>
+          <t>957843678.574127</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2171.498</t>
+          <t>1286468965.17748</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2289.441</t>
+          <t>1468388292.76209</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2215.011</t>
+          <t>1830620414.91559</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2286.728</t>
+          <t>1625976892.07124</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2331.579</t>
+          <t>1265230358.28554</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2355.983</t>
+          <t>1396198778.28728</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2344.863</t>
+          <t>1303365841.30639</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2371.724</t>
+          <t>1412327694.77259</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2501.374</t>
+          <t>1310590718.43802</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2324.75</t>
+          <t>1352478171.16035</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2214.72</t>
+          <t>1117224943.61226</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1870.716</t>
+          <t>961020734.190941</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1727.862</t>
+          <t>1285865998.59069</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1632.157</t>
+          <t>1588048472.16978</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1739.721</t>
+          <t>1176140787.79197</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>1894.692</t>
+          <t>1163130250.5308</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>1792.556</t>
+          <t>1199832195.22864</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2012.28</t>
+          <t>1111043939.79128</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>1907.56</t>
+          <t>1226799435.21816</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>2169.817</t>
+          <t>1396621916.69418</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2309.447</t>
+          <t>1389758989.94721</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2275.276</t>
+          <t>1569039932.51232</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2356.7</t>
+          <t>998659979.925243</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2482.216</t>
+          <t>-256.426454408087</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1295.763</t>
+          <t>-554.462809717119</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1413.372</t>
+          <t>-680.62080883153</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1450.843</t>
+          <t>-1010.1136805045</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1384.943</t>
+          <t>-906.841323530115</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1506.815</t>
+          <t>-897.959304602637</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1561.965</t>
+          <t>-1266.05267086429</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1595.346</t>
+          <t>-1338.77880125489</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1750.087</t>
+          <t>-1703.8898805278</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1749.95</t>
+          <t>-2324.20055240755</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1746.657</t>
+          <t>-2555.61753192073</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1863.841</t>
+          <t>-4638.48699730611</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1946.868</t>
+          <t>-5646.41027239676</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1832.046</t>
+          <t>-4036.94368065674</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1791.426</t>
+          <t>-491.524787161899</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1469.006</t>
+          <t>-493.693157188913</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1366.186</t>
+          <t>-1544.32076513496</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1262.17</t>
+          <t>-1532.02047279707</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>1373.036</t>
+          <t>-1299.06360996319</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>1698.619</t>
+          <t>-907.784938301862</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>1619.831</t>
+          <t>-553.754565606895</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>1802.726</t>
+          <t>109.136116297486</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>1708.058</t>
+          <t>-228.297301453437</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>1936.419</t>
+          <t>-301.438119902389</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2066.989</t>
+          <t>-333.900156656356</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2065.269</t>
+          <t>-525.13522172377</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2124.189</t>
+          <t>-741.497565826883</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2648.059</t>
+          <t>-385025622.429125</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2542.209</t>
+          <t>257652670.245304</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2704.972</t>
+          <t>-190799344.126572</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2561.785</t>
+          <t>-315908236.250389</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2795.749</t>
+          <t>-677177927.222206</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2897.86</t>
+          <t>-815133367.140494</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2707.84</t>
+          <t>-1166169633.03956</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2709.126</t>
+          <t>-1013783745.57527</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2686.644</t>
+          <t>-711238758.530676</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2966.754</t>
+          <t>-811537314.259543</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2931.368</t>
+          <t>-627906841.836284</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2937.403</t>
+          <t>-852064460.870734</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2993.724</t>
+          <t>-732999313.017435</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2947.867</t>
+          <t>-785905564.228773</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2605.647</t>
+          <t>-552077828.717326</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2143.182</t>
+          <t>-419439468.066226</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2148.327</t>
+          <t>-713600776.562517</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2205.401</t>
+          <t>-943725703.442942</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2072.214</t>
+          <t>-555776284.67686</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2142.25</t>
+          <t>-509059290.475628</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>2084.809</t>
+          <t>-562748829.746108</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2183.742</t>
+          <t>-437465890.172815</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2148.381</t>
+          <t>-506253462.874126</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>2503.177</t>
+          <t>-563658162.648755</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2517.726</t>
+          <t>-567786850.54959</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2582.941</t>
+          <t>-712780346.101438</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2531.142</t>
+          <t>-362703516.465668</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>2494.81058277674</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>2949.6654731842</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>3352.43998782287</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>3458.54247781896</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>3407.9021459662</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>4036.67093006513</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>4324.6143376369</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>4277.96719149274</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>4028.15466472069</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>4347.39613017587</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>5056.86605019371</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>6937.46576137407</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>8613.67514060411</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>10095.7432977929</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>7621.69788040325</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>6746.3113368322</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>7992.18235102858</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>7961.18449355626</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>8274.98592772917</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>7687.22188257711</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>8607.20909980048</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>8012.62486684798</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>8992.50814463814</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>9568.95438438591</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>9383.83503227954</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>9702.36718781411</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>9879.63289863551</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1680.062</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>1715.021</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>1742.371</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>1655.599</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>1486.981</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>1534.224</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1417.246</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>1502.796</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>1553.394</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>1565.821</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>1559.424</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>1514.145</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>1546.655</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>1412.184</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>1362.007</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>1118.273</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>1011.926</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>1046.91</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>1073.77</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>1153.152</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>1065.081</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>1209.726</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>1124.83</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>1301.878</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>1381.817</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>1324.942</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>1393.147</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>3436.50490543912</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>3860.19581643201</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>4608.4914821859</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>4465.5646961974</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>4710.3768903168</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>5540.62405645469</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>5831.20702129323</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>6214.50500702787</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>6020.11786080372</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>5561.33396725271</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>7455.7965754</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>10977.9526284365</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14348.3907668158</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>15637.0963318686</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>11587.4665744588</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>10500.4107620702</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11006.8409300867</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>11924.8208974308</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>12785.9120942154</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>12424.9072756154</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>13759.9585054562</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>12719.1170600703</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14130.2925712715</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>15666.7956884149</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>15722.3997659593</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>16337.72713499</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>16669.1956998692</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>912.575</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>671.541</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>726.174</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>706.762</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>770.572</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>887.92</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>877.911</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>957.03</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>677.519</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>503.818</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>597.033</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>899.954</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>886.897</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>797.721</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>592.165</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>503.502</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>576.789</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>516.818</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>557.014</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>492.342</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>566.35</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>449.942</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>558.554</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>649.255</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>641.469</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>653.027</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>524.11</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>92.95</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>94.63</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>105.28</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>79.73</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>69.7</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>77.92</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>158.31</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>247.34</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>192.56</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>107.1</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>119.51</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>129.66</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>202.52</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>191.76</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>136.86</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>144.22</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>146.5</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>245.01</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>186.01</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>300.66</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>205.8</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>198.25</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>222.23</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>216.26</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>305.29</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2186.334</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>149.405</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>15328.666</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>81.589</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>50.659</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>460.361</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>35.814</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>38.272</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>515.66</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>30.299</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>21.072</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>155.968</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>149350.56</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>22.327</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>18.26</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>16.675</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>13.66</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>29.805</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>13.22</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>11.23</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>9.932</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>64.388</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>9.07</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10.275</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>11.117</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>9.819</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>10.683</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1215.02422900642</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1562.46098712436</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1797.85551747757</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2848.01313047936</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>3201.38404187945</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>4243.25540955905</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>4814.49660468994</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>5509.32952447075</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>6270.10672983802</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>7939.44135045769</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>8457.24153558281</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>9246.79138863753</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>12571.5769997424</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>13081.1477053759</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>10693.9914845124</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>10734.3335883536</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>13016.5162270156</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>13884.3957702002</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>14091.0717700905</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>15474.2392837641</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>15156.4937357479</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>17116.3314435844</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>17788.3975971732</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>18956.62394023</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>20335.5563297619</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>20994.594676978</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>21917.0488980176</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2482216265.72787</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1295763000.00032</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1413371999.9997</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1450842999.99928</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1384943000.00073</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1506814999.9995</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1561964999.99967</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1595345999.99932</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1750087000.00023</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1749949999.99952</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>1746656999.99973</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>1863841000.00029</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>1946868000.00004</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>1832046000.00036</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1791426000.00056</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1469006000.00035</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1366185999.99976</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1262170000.00013</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>1373036000.00011</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>1698618673.20662</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>1619830947.6713</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>1802725797.06564</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>1708057658.63376</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>1936419320.28309</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2066989403.51473</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>2065268818.75981</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>2124189203.40553</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2795286475.21463</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2321361000.00083</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2355422000.00023</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2319762999.99983</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2171498000.00042</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2289440999.99968</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2215011000.00013</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2286727999.99985</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2331579000.00038</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2355982999.99966</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2344862999.99993</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2371724000.00041</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2501374000.00012</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2324750000.00022</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2214720000.00059</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1870716000.0002</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1727861999.99982</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1632157000.00004</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>1739721000.00004</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1894692481.38113</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>1792555514.90341</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>2012280462.98664</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>1907559647.68816</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>2169817151.03983</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2309446869.61626</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>2275275692.9776</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>2356700127.12889</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1680061632.02226</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1715021155.42214</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1742371170.92448</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1655599317.7131</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1486981311.13352</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1534224253.10563</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1417246279.20295</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1502795621.06196</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1553394037.96908</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1565820507.37857</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1559423979.55232</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1514145315.53512</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1546655379.8852</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>1412184378.50881</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1362007285.17531</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1118273407.08978</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1011925929.17988</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1046910164.83589</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>1073769595.79744</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>1153151837.15891</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>1065080566.81118</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>1209726123.98216</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>1124830117.29928</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>1301877728.42393</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>1381816749.00074</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>1324941694.3762</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>1393147293.33752</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1338303.34095889</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1105200.00000002</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1051100.00000012</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1033900.00000003</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>964699.999999967</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1016100.00000034</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>984200.000000064</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1004499.99999986</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1027800.00000001</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1049699.9999998</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1072200.00000003</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1079000.0000003</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1138400.00000018</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>1073300.00000006</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1054599.99999991</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>908200.000000136</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>850399.999999986</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>801900.000000093</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>853299.99999988</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>922343.554213044</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>870945.717114222</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>976288.062661292</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>922894.594944522</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>1050849.4514973</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>1111608.93157494</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>1097333.32138247</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>1133904.50949482</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1185773.25689473</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>876499.999999758</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>841799.999999682</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>841000.000000356</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>793499.999999864</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>849400.000000323</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>843500.000000016</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>858399.999999827</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>897900.000000066</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>912599.999999746</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>933400.000000039</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>960800.000000336</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1012400.00000021</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>961400.000000025</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>953099.999999949</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>809800.000000105</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>760400.000000027</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>712500.00000015</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>763499.999999879</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>825928.76051265</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>786933.158179544</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>874342.650957085</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>826045.328155102</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>937774.68873516</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>994125.145982931</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>995551.87978817</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>1021804.88277301</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2795286475.21463</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2321361000.00083</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2355422000.00023</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2319762999.99983</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2171498000.00042</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2289440999.99968</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2215011000.00013</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2286727999.99985</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2331579000.00038</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2355982999.99966</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2344862999.99993</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2371724000.00041</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2501374000.00012</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>2324750000.00022</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2214720000.00059</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1870716000.0002</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1727861999.99982</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1632157000.00004</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>1739721000.00004</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>1894692481.38113</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>1792555514.90341</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>2012280462.98664</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>1907559647.68816</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>2169817151.03983</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2309446869.61626</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>2275275692.9776</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>2356700127.12889</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2482216265.72787</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1295763000.00032</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1413371999.9997</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1450842999.99928</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1384943000.00073</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1506814999.9995</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1561964999.99967</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1595345999.99932</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1750087000.00023</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1749949999.99952</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>1746656999.99973</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>1863841000.00029</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>1946868000.00004</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>1832046000.00036</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1791426000.00056</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1469006000.00035</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1366185999.99976</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1262170000.00013</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>1373036000.00011</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>1698618673.20662</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>1619830947.6713</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>1802725797.06564</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>1708057658.63376</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>1936419320.28309</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2066989403.51473</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>2065268818.75981</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>2124189203.40553</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>10092.7760760491</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>11576.3214940614</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>14162.1836367563</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>15532.8452355142</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>17038.0415870432</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>20715.6937793896</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>22021.0448035914</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>23908.5059002517</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>24731.2298382373</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>29185.2449255487</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>34601.9322028702</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>43211.9555584388</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>56394.2909307087</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>60829.757645841</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>47785.4170412707</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>46527.4557360349</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>50789.8610878964</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>55556.1823665037</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>57145.8323451853</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>57130.9869802335</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>60807.2053418092</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>61175.4074086199</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>67348.8416131024</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>72358.5169559256</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>74553.628149456</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>76964.6811569552</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>78835.3425184152</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3925.26523401912</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>4285.87721043147</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>5357.12238600568</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>5096.95552613895</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>5582.71785844978</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>6464.73769415185</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>6785.97483760086</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>7048.77559612775</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>6651.34213657969</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>6464.96224295817</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>8501.53865421219</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>12073.7266463589</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>15575.1179943011</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>17161.86685621</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>12781.9039134728</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>11673.3258842491</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>12562.4332382961</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>13548.5971474789</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>14416.7155599072</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>13864.5515986586</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>15387.5386290057</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>14412.8525318407</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>15754.5387017698</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>17297.9273861954</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>17562.6948377256</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>17962.5365037733</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>18167.8818789915</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
